--- a/Treinamento/EmissaoFielDepositario - Copy.xlsx
+++ b/Treinamento/EmissaoFielDepositario - Copy.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{543DFBE3-8AE0-447D-B680-EB6AB3D1851F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7115ABF-D3A6-4E55-9719-0EBD7A5D3E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FIEL" r:id="rId1" sheetId="1"/>
-    <sheet name="P3" r:id="rId2" sheetId="2"/>
+    <sheet name="FIEL" sheetId="1" r:id="rId1"/>
+    <sheet name="P3" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">FIEL!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FIEL!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14269" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="187">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -596,7 +596,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -661,42 +660,42 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{9A64B6ED-0441-41B2-A6F4-AEA4AC2561AE}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -713,10 +712,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -751,7 +750,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -803,7 +802,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -914,21 +913,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -945,7 +944,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -997,36 +996,36 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:P967"/>
+  <dimension ref="A1:O606"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="13.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="23.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="35.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="5" width="24.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="5" width="21.28515625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="8" width="48.42578125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="8" width="32.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="5" width="24.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="5" width="18.42578125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="5" width="17.85546875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="5" width="16.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="19.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="41.42578125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="56.0" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="28.42578125" collapsed="true"/>
-    <col min="16" max="16384" style="5" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="23.42578125" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.85546875" style="5" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.5703125" style="5" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="21.28515625" style="5" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="48.42578125" style="8" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="32.28515625" style="8" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="24.28515625" style="5" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.42578125" style="5" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.85546875" style="5" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="16.7109375" style="5" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="19" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="41.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="56" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="28.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="16384" width="9.140625" style="5" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21147,5108 +21146,54 @@
         <v>15</v>
       </c>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A607" s="5"/>
-      <c r="K607" s="5">
-        <v>0</v>
-      </c>
-      <c r="L607" s="5">
-        <v>61</v>
-      </c>
-      <c r="M607" s="5"/>
-      <c r="N607" s="5"/>
-      <c r="O607" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A608" s="5"/>
-      <c r="K608" s="5">
-        <v>0</v>
-      </c>
-      <c r="L608" s="5">
-        <v>61</v>
-      </c>
-      <c r="M608" s="5"/>
-      <c r="N608" s="5"/>
-      <c r="O608" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A609" s="5"/>
-      <c r="K609" s="5">
-        <v>0</v>
-      </c>
-      <c r="L609" s="5">
-        <v>61</v>
-      </c>
-      <c r="M609" s="5"/>
-      <c r="N609" s="5"/>
-      <c r="O609" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A610" s="5"/>
-      <c r="K610" s="5">
-        <v>0</v>
-      </c>
-      <c r="L610" s="5">
-        <v>61</v>
-      </c>
-      <c r="M610" s="5"/>
-      <c r="N610" s="5"/>
-      <c r="O610" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A611" s="5"/>
-      <c r="K611" s="5">
-        <v>0</v>
-      </c>
-      <c r="L611" s="5">
-        <v>61</v>
-      </c>
-      <c r="M611" s="5"/>
-      <c r="N611" s="5"/>
-      <c r="O611" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A612" s="5"/>
-      <c r="K612" s="5">
-        <v>0</v>
-      </c>
-      <c r="L612" s="5">
-        <v>61</v>
-      </c>
-      <c r="M612" s="5"/>
-      <c r="N612" s="5"/>
-      <c r="O612" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A613" s="5"/>
-      <c r="K613" s="5">
-        <v>0</v>
-      </c>
-      <c r="L613" s="5">
-        <v>61</v>
-      </c>
-      <c r="M613" s="5"/>
-      <c r="N613" s="5"/>
-      <c r="O613" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A614" s="5"/>
-      <c r="K614" s="5">
-        <v>0</v>
-      </c>
-      <c r="L614" s="5">
-        <v>61</v>
-      </c>
-      <c r="M614" s="5"/>
-      <c r="N614" s="5"/>
-      <c r="O614" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A615" s="5"/>
-      <c r="K615" s="5">
-        <v>0</v>
-      </c>
-      <c r="L615" s="5">
-        <v>61</v>
-      </c>
-      <c r="M615" s="5"/>
-      <c r="N615" s="5"/>
-      <c r="O615" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A616" s="5"/>
-      <c r="K616" s="5">
-        <v>0</v>
-      </c>
-      <c r="L616" s="5">
-        <v>61</v>
-      </c>
-      <c r="M616" s="5"/>
-      <c r="N616" s="5"/>
-      <c r="O616" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A617" s="5"/>
-      <c r="K617" s="5">
-        <v>0</v>
-      </c>
-      <c r="L617" s="5">
-        <v>61</v>
-      </c>
-      <c r="M617" s="5"/>
-      <c r="N617" s="5"/>
-      <c r="O617" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A618" s="5"/>
-      <c r="K618" s="5">
-        <v>0</v>
-      </c>
-      <c r="L618" s="5">
-        <v>61</v>
-      </c>
-      <c r="M618" s="5"/>
-      <c r="N618" s="5"/>
-      <c r="O618" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A619" s="5"/>
-      <c r="K619" s="5">
-        <v>0</v>
-      </c>
-      <c r="L619" s="5">
-        <v>61</v>
-      </c>
-      <c r="M619" s="5"/>
-      <c r="N619" s="5"/>
-      <c r="O619" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A620" s="5"/>
-      <c r="K620" s="5">
-        <v>0</v>
-      </c>
-      <c r="L620" s="5">
-        <v>61</v>
-      </c>
-      <c r="M620" s="5"/>
-      <c r="N620" s="5"/>
-      <c r="O620" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A621" s="5"/>
-      <c r="K621" s="5">
-        <v>0</v>
-      </c>
-      <c r="L621" s="5">
-        <v>61</v>
-      </c>
-      <c r="M621" s="5"/>
-      <c r="N621" s="5"/>
-      <c r="O621" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A622" s="5"/>
-      <c r="K622" s="5">
-        <v>0</v>
-      </c>
-      <c r="L622" s="5">
-        <v>61</v>
-      </c>
-      <c r="M622" s="5"/>
-      <c r="N622" s="5"/>
-      <c r="O622" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A623" s="5"/>
-      <c r="K623" s="5">
-        <v>0</v>
-      </c>
-      <c r="L623" s="5">
-        <v>61</v>
-      </c>
-      <c r="M623" s="5"/>
-      <c r="N623" s="5"/>
-      <c r="O623" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A624" s="5"/>
-      <c r="K624" s="5">
-        <v>0</v>
-      </c>
-      <c r="L624" s="5">
-        <v>61</v>
-      </c>
-      <c r="M624" s="5"/>
-      <c r="N624" s="5"/>
-      <c r="O624" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A625" s="5"/>
-      <c r="K625" s="5">
-        <v>0</v>
-      </c>
-      <c r="L625" s="5">
-        <v>61</v>
-      </c>
-      <c r="M625" s="5"/>
-      <c r="N625" s="5"/>
-      <c r="O625" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A626" s="5"/>
-      <c r="K626" s="5">
-        <v>0</v>
-      </c>
-      <c r="L626" s="5">
-        <v>61</v>
-      </c>
-      <c r="M626" s="5"/>
-      <c r="N626" s="5"/>
-      <c r="O626" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A627" s="5"/>
-      <c r="K627" s="5">
-        <v>0</v>
-      </c>
-      <c r="L627" s="5">
-        <v>61</v>
-      </c>
-      <c r="M627" s="5"/>
-      <c r="N627" s="5"/>
-      <c r="O627" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A628" s="5"/>
-      <c r="K628" s="5">
-        <v>0</v>
-      </c>
-      <c r="L628" s="5">
-        <v>61</v>
-      </c>
-      <c r="M628" s="5"/>
-      <c r="N628" s="5"/>
-      <c r="O628" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A629" s="5"/>
-      <c r="K629" s="5">
-        <v>0</v>
-      </c>
-      <c r="L629" s="5">
-        <v>61</v>
-      </c>
-      <c r="M629" s="5"/>
-      <c r="N629" s="5"/>
-      <c r="O629" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A630" s="5"/>
-      <c r="K630" s="5">
-        <v>0</v>
-      </c>
-      <c r="L630" s="5">
-        <v>61</v>
-      </c>
-      <c r="M630" s="5"/>
-      <c r="N630" s="5"/>
-      <c r="O630" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A631" s="5"/>
-      <c r="K631" s="5">
-        <v>0</v>
-      </c>
-      <c r="L631" s="5">
-        <v>61</v>
-      </c>
-      <c r="M631" s="5"/>
-      <c r="N631" s="5"/>
-      <c r="O631" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A632" s="5"/>
-      <c r="K632" s="5">
-        <v>0</v>
-      </c>
-      <c r="L632" s="5">
-        <v>61</v>
-      </c>
-      <c r="M632" s="5"/>
-      <c r="N632" s="5"/>
-      <c r="O632" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A633" s="5"/>
-      <c r="K633" s="5">
-        <v>0</v>
-      </c>
-      <c r="L633" s="5">
-        <v>61</v>
-      </c>
-      <c r="M633" s="5"/>
-      <c r="N633" s="5"/>
-      <c r="O633" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A634" s="5"/>
-      <c r="K634" s="5">
-        <v>0</v>
-      </c>
-      <c r="L634" s="5">
-        <v>61</v>
-      </c>
-      <c r="M634" s="5"/>
-      <c r="N634" s="5"/>
-      <c r="O634" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A635" s="5"/>
-      <c r="K635" s="5">
-        <v>0</v>
-      </c>
-      <c r="L635" s="5">
-        <v>61</v>
-      </c>
-      <c r="M635" s="5"/>
-      <c r="N635" s="5"/>
-      <c r="O635" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A636" s="5"/>
-      <c r="K636" s="5">
-        <v>0</v>
-      </c>
-      <c r="L636" s="5">
-        <v>61</v>
-      </c>
-      <c r="M636" s="5"/>
-      <c r="N636" s="5"/>
-      <c r="O636" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A637" s="5"/>
-      <c r="K637" s="5">
-        <v>0</v>
-      </c>
-      <c r="L637" s="5">
-        <v>61</v>
-      </c>
-      <c r="M637" s="5"/>
-      <c r="N637" s="5"/>
-      <c r="O637" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A638" s="5"/>
-      <c r="K638" s="5">
-        <v>0</v>
-      </c>
-      <c r="L638" s="5">
-        <v>61</v>
-      </c>
-      <c r="M638" s="5"/>
-      <c r="N638" s="5"/>
-      <c r="O638" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A639" s="5"/>
-      <c r="K639" s="5">
-        <v>0</v>
-      </c>
-      <c r="L639" s="5">
-        <v>61</v>
-      </c>
-      <c r="M639" s="5"/>
-      <c r="N639" s="5"/>
-      <c r="O639" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A640" s="5"/>
-      <c r="K640" s="5">
-        <v>0</v>
-      </c>
-      <c r="L640" s="5">
-        <v>61</v>
-      </c>
-      <c r="M640" s="5"/>
-      <c r="N640" s="5"/>
-      <c r="O640" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A641" s="5"/>
-      <c r="K641" s="5">
-        <v>0</v>
-      </c>
-      <c r="L641" s="5">
-        <v>61</v>
-      </c>
-      <c r="M641" s="5"/>
-      <c r="N641" s="5"/>
-      <c r="O641" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A642" s="5"/>
-      <c r="K642" s="5">
-        <v>0</v>
-      </c>
-      <c r="L642" s="5">
-        <v>61</v>
-      </c>
-      <c r="M642" s="5"/>
-      <c r="N642" s="5"/>
-      <c r="O642" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A643" s="5"/>
-      <c r="K643" s="5">
-        <v>0</v>
-      </c>
-      <c r="L643" s="5">
-        <v>61</v>
-      </c>
-      <c r="M643" s="5"/>
-      <c r="N643" s="5"/>
-      <c r="O643" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A644" s="5"/>
-      <c r="K644" s="5">
-        <v>0</v>
-      </c>
-      <c r="L644" s="5">
-        <v>61</v>
-      </c>
-      <c r="M644" s="5"/>
-      <c r="N644" s="5"/>
-      <c r="O644" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A645" s="5"/>
-      <c r="K645" s="5">
-        <v>0</v>
-      </c>
-      <c r="L645" s="5">
-        <v>61</v>
-      </c>
-      <c r="M645" s="5"/>
-      <c r="N645" s="5"/>
-      <c r="O645" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A646" s="5"/>
-      <c r="K646" s="5">
-        <v>0</v>
-      </c>
-      <c r="L646" s="5">
-        <v>61</v>
-      </c>
-      <c r="M646" s="5"/>
-      <c r="N646" s="5"/>
-      <c r="O646" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A647" s="5"/>
-      <c r="K647" s="5">
-        <v>0</v>
-      </c>
-      <c r="L647" s="5">
-        <v>61</v>
-      </c>
-      <c r="M647" s="5"/>
-      <c r="N647" s="5"/>
-      <c r="O647" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A648" s="5"/>
-      <c r="K648" s="5">
-        <v>0</v>
-      </c>
-      <c r="L648" s="5">
-        <v>61</v>
-      </c>
-      <c r="M648" s="5"/>
-      <c r="N648" s="5"/>
-      <c r="O648" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A649" s="5"/>
-      <c r="K649" s="5">
-        <v>0</v>
-      </c>
-      <c r="L649" s="5">
-        <v>61</v>
-      </c>
-      <c r="M649" s="5"/>
-      <c r="N649" s="5"/>
-      <c r="O649" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A650" s="5"/>
-      <c r="K650" s="5">
-        <v>0</v>
-      </c>
-      <c r="L650" s="5">
-        <v>61</v>
-      </c>
-      <c r="M650" s="5"/>
-      <c r="N650" s="5"/>
-      <c r="O650" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A651" s="5"/>
-      <c r="K651" s="5">
-        <v>0</v>
-      </c>
-      <c r="L651" s="5">
-        <v>61</v>
-      </c>
-      <c r="M651" s="5"/>
-      <c r="N651" s="5"/>
-      <c r="O651" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A652" s="5"/>
-      <c r="K652" s="5">
-        <v>0</v>
-      </c>
-      <c r="L652" s="5">
-        <v>61</v>
-      </c>
-      <c r="M652" s="5"/>
-      <c r="N652" s="5"/>
-      <c r="O652" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A653" s="5"/>
-      <c r="K653" s="5">
-        <v>0</v>
-      </c>
-      <c r="L653" s="5">
-        <v>61</v>
-      </c>
-      <c r="M653" s="5"/>
-      <c r="N653" s="5"/>
-      <c r="O653" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A654" s="5"/>
-      <c r="K654" s="5">
-        <v>0</v>
-      </c>
-      <c r="L654" s="5">
-        <v>61</v>
-      </c>
-      <c r="M654" s="5"/>
-      <c r="N654" s="5"/>
-      <c r="O654" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A655" s="5"/>
-      <c r="K655" s="5">
-        <v>0</v>
-      </c>
-      <c r="L655" s="5">
-        <v>61</v>
-      </c>
-      <c r="M655" s="5"/>
-      <c r="N655" s="5"/>
-      <c r="O655" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A656" s="5"/>
-      <c r="K656" s="5">
-        <v>0</v>
-      </c>
-      <c r="L656" s="5">
-        <v>61</v>
-      </c>
-      <c r="M656" s="5"/>
-      <c r="N656" s="5"/>
-      <c r="O656" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A657" s="5"/>
-      <c r="K657" s="5">
-        <v>0</v>
-      </c>
-      <c r="L657" s="5">
-        <v>61</v>
-      </c>
-      <c r="M657" s="5"/>
-      <c r="N657" s="5"/>
-      <c r="O657" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A658" s="5"/>
-      <c r="K658" s="5">
-        <v>0</v>
-      </c>
-      <c r="L658" s="5">
-        <v>61</v>
-      </c>
-      <c r="M658" s="5"/>
-      <c r="N658" s="5"/>
-      <c r="O658" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A659" s="5"/>
-      <c r="K659" s="5">
-        <v>0</v>
-      </c>
-      <c r="L659" s="5">
-        <v>61</v>
-      </c>
-      <c r="M659" s="5"/>
-      <c r="N659" s="5"/>
-      <c r="O659" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A660" s="5"/>
-      <c r="K660" s="5">
-        <v>0</v>
-      </c>
-      <c r="L660" s="5">
-        <v>61</v>
-      </c>
-      <c r="M660" s="5"/>
-      <c r="N660" s="5"/>
-      <c r="O660" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A661" s="5"/>
-      <c r="K661" s="5">
-        <v>0</v>
-      </c>
-      <c r="L661" s="5">
-        <v>61</v>
-      </c>
-      <c r="M661" s="5"/>
-      <c r="N661" s="5"/>
-      <c r="O661" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A662" s="5"/>
-      <c r="K662" s="5">
-        <v>0</v>
-      </c>
-      <c r="L662" s="5">
-        <v>61</v>
-      </c>
-      <c r="M662" s="5"/>
-      <c r="N662" s="5"/>
-      <c r="O662" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A663" s="5"/>
-      <c r="K663" s="5">
-        <v>0</v>
-      </c>
-      <c r="L663" s="5">
-        <v>61</v>
-      </c>
-      <c r="M663" s="5"/>
-      <c r="N663" s="5"/>
-      <c r="O663" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A664" s="5"/>
-      <c r="K664" s="5">
-        <v>0</v>
-      </c>
-      <c r="L664" s="5">
-        <v>61</v>
-      </c>
-      <c r="M664" s="5"/>
-      <c r="N664" s="5"/>
-      <c r="O664" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A665" s="5"/>
-      <c r="K665" s="5">
-        <v>0</v>
-      </c>
-      <c r="L665" s="5">
-        <v>61</v>
-      </c>
-      <c r="M665" s="5"/>
-      <c r="N665" s="5"/>
-      <c r="O665" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A666" s="5"/>
-      <c r="K666" s="5">
-        <v>0</v>
-      </c>
-      <c r="L666" s="5">
-        <v>61</v>
-      </c>
-      <c r="M666" s="5"/>
-      <c r="N666" s="5"/>
-      <c r="O666" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A667" s="5"/>
-      <c r="K667" s="5">
-        <v>0</v>
-      </c>
-      <c r="L667" s="5">
-        <v>61</v>
-      </c>
-      <c r="M667" s="5"/>
-      <c r="N667" s="5"/>
-      <c r="O667" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A668" s="5"/>
-      <c r="K668" s="5">
-        <v>0</v>
-      </c>
-      <c r="L668" s="5">
-        <v>61</v>
-      </c>
-      <c r="M668" s="5"/>
-      <c r="N668" s="5"/>
-      <c r="O668" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A669" s="5"/>
-      <c r="K669" s="5">
-        <v>0</v>
-      </c>
-      <c r="L669" s="5">
-        <v>61</v>
-      </c>
-      <c r="M669" s="5"/>
-      <c r="N669" s="5"/>
-      <c r="O669" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A670" s="5"/>
-      <c r="K670" s="5">
-        <v>0</v>
-      </c>
-      <c r="L670" s="5">
-        <v>61</v>
-      </c>
-      <c r="M670" s="5"/>
-      <c r="N670" s="5"/>
-      <c r="O670" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A671" s="5"/>
-      <c r="K671" s="5">
-        <v>0</v>
-      </c>
-      <c r="L671" s="5">
-        <v>61</v>
-      </c>
-      <c r="M671" s="5"/>
-      <c r="N671" s="5"/>
-      <c r="O671" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A672" s="5"/>
-      <c r="K672" s="5">
-        <v>0</v>
-      </c>
-      <c r="L672" s="5">
-        <v>61</v>
-      </c>
-      <c r="M672" s="5"/>
-      <c r="N672" s="5"/>
-      <c r="O672" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A673" s="5"/>
-      <c r="K673" s="5">
-        <v>0</v>
-      </c>
-      <c r="L673" s="5">
-        <v>61</v>
-      </c>
-      <c r="M673" s="5"/>
-      <c r="N673" s="5"/>
-      <c r="O673" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A674" s="5"/>
-      <c r="K674" s="5">
-        <v>0</v>
-      </c>
-      <c r="L674" s="5">
-        <v>61</v>
-      </c>
-      <c r="M674" s="5"/>
-      <c r="N674" s="5"/>
-      <c r="O674" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A675" s="5"/>
-      <c r="K675" s="5">
-        <v>0</v>
-      </c>
-      <c r="L675" s="5">
-        <v>61</v>
-      </c>
-      <c r="M675" s="5"/>
-      <c r="N675" s="5"/>
-      <c r="O675" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A676" s="5"/>
-      <c r="K676" s="5">
-        <v>0</v>
-      </c>
-      <c r="L676" s="5">
-        <v>61</v>
-      </c>
-      <c r="M676" s="5"/>
-      <c r="N676" s="5"/>
-      <c r="O676" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A677" s="5"/>
-      <c r="K677" s="5">
-        <v>0</v>
-      </c>
-      <c r="L677" s="5">
-        <v>61</v>
-      </c>
-      <c r="M677" s="5"/>
-      <c r="N677" s="5"/>
-      <c r="O677" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A678" s="5"/>
-      <c r="K678" s="5">
-        <v>0</v>
-      </c>
-      <c r="L678" s="5">
-        <v>61</v>
-      </c>
-      <c r="M678" s="5"/>
-      <c r="N678" s="5"/>
-      <c r="O678" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A679" s="5"/>
-      <c r="K679" s="5">
-        <v>0</v>
-      </c>
-      <c r="L679" s="5">
-        <v>61</v>
-      </c>
-      <c r="M679" s="5"/>
-      <c r="N679" s="5"/>
-      <c r="O679" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A680" s="5"/>
-      <c r="K680" s="5">
-        <v>0</v>
-      </c>
-      <c r="L680" s="5">
-        <v>61</v>
-      </c>
-      <c r="M680" s="5"/>
-      <c r="N680" s="5"/>
-      <c r="O680" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A681" s="5"/>
-      <c r="K681" s="5">
-        <v>0</v>
-      </c>
-      <c r="L681" s="5">
-        <v>61</v>
-      </c>
-      <c r="M681" s="5"/>
-      <c r="N681" s="5"/>
-      <c r="O681" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A682" s="5"/>
-      <c r="K682" s="5">
-        <v>0</v>
-      </c>
-      <c r="L682" s="5">
-        <v>61</v>
-      </c>
-      <c r="M682" s="5"/>
-      <c r="N682" s="5"/>
-      <c r="O682" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A683" s="5"/>
-      <c r="K683" s="5">
-        <v>0</v>
-      </c>
-      <c r="L683" s="5">
-        <v>61</v>
-      </c>
-      <c r="M683" s="5"/>
-      <c r="N683" s="5"/>
-      <c r="O683" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A684" s="5"/>
-      <c r="K684" s="5">
-        <v>0</v>
-      </c>
-      <c r="L684" s="5">
-        <v>61</v>
-      </c>
-      <c r="M684" s="5"/>
-      <c r="N684" s="5"/>
-      <c r="O684" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A685" s="5"/>
-      <c r="K685" s="5">
-        <v>0</v>
-      </c>
-      <c r="L685" s="5">
-        <v>61</v>
-      </c>
-      <c r="M685" s="5"/>
-      <c r="N685" s="5"/>
-      <c r="O685" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A686" s="5"/>
-      <c r="K686" s="5">
-        <v>0</v>
-      </c>
-      <c r="L686" s="5">
-        <v>61</v>
-      </c>
-      <c r="M686" s="5"/>
-      <c r="N686" s="5"/>
-      <c r="O686" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A687" s="5"/>
-      <c r="K687" s="5">
-        <v>0</v>
-      </c>
-      <c r="L687" s="5">
-        <v>61</v>
-      </c>
-      <c r="M687" s="5"/>
-      <c r="N687" s="5"/>
-      <c r="O687" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A688" s="5"/>
-      <c r="K688" s="5">
-        <v>0</v>
-      </c>
-      <c r="L688" s="5">
-        <v>61</v>
-      </c>
-      <c r="M688" s="5"/>
-      <c r="N688" s="5"/>
-      <c r="O688" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A689" s="5"/>
-      <c r="K689" s="5">
-        <v>0</v>
-      </c>
-      <c r="L689" s="5">
-        <v>61</v>
-      </c>
-      <c r="M689" s="5"/>
-      <c r="N689" s="5"/>
-      <c r="O689" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A690" s="5"/>
-      <c r="K690" s="5">
-        <v>0</v>
-      </c>
-      <c r="L690" s="5">
-        <v>61</v>
-      </c>
-      <c r="M690" s="5"/>
-      <c r="N690" s="5"/>
-      <c r="O690" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A691" s="5"/>
-      <c r="K691" s="5">
-        <v>0</v>
-      </c>
-      <c r="L691" s="5">
-        <v>61</v>
-      </c>
-      <c r="M691" s="5"/>
-      <c r="N691" s="5"/>
-      <c r="O691" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A692" s="5"/>
-      <c r="K692" s="5">
-        <v>0</v>
-      </c>
-      <c r="L692" s="5">
-        <v>61</v>
-      </c>
-      <c r="M692" s="5"/>
-      <c r="N692" s="5"/>
-      <c r="O692" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A693" s="5"/>
-      <c r="K693" s="5">
-        <v>0</v>
-      </c>
-      <c r="L693" s="5">
-        <v>61</v>
-      </c>
-      <c r="M693" s="5"/>
-      <c r="N693" s="5"/>
-      <c r="O693" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A694" s="5"/>
-      <c r="K694" s="5">
-        <v>0</v>
-      </c>
-      <c r="L694" s="5">
-        <v>61</v>
-      </c>
-      <c r="M694" s="5"/>
-      <c r="N694" s="5"/>
-      <c r="O694" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A695" s="5"/>
-      <c r="K695" s="5">
-        <v>0</v>
-      </c>
-      <c r="L695" s="5">
-        <v>61</v>
-      </c>
-      <c r="M695" s="5"/>
-      <c r="N695" s="5"/>
-      <c r="O695" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A696" s="5"/>
-      <c r="K696" s="5">
-        <v>0</v>
-      </c>
-      <c r="L696" s="5">
-        <v>61</v>
-      </c>
-      <c r="M696" s="5"/>
-      <c r="N696" s="5"/>
-      <c r="O696" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A697" s="5"/>
-      <c r="K697" s="5">
-        <v>0</v>
-      </c>
-      <c r="L697" s="5">
-        <v>61</v>
-      </c>
-      <c r="M697" s="5"/>
-      <c r="N697" s="5"/>
-      <c r="O697" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A698" s="5"/>
-      <c r="K698" s="5">
-        <v>0</v>
-      </c>
-      <c r="L698" s="5">
-        <v>61</v>
-      </c>
-      <c r="M698" s="5"/>
-      <c r="N698" s="5"/>
-      <c r="O698" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A699" s="5"/>
-      <c r="K699" s="5">
-        <v>0</v>
-      </c>
-      <c r="L699" s="5">
-        <v>61</v>
-      </c>
-      <c r="M699" s="5"/>
-      <c r="N699" s="5"/>
-      <c r="O699" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A700" s="5"/>
-      <c r="K700" s="5">
-        <v>0</v>
-      </c>
-      <c r="L700" s="5">
-        <v>61</v>
-      </c>
-      <c r="M700" s="5"/>
-      <c r="N700" s="5"/>
-      <c r="O700" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A701" s="5"/>
-      <c r="K701" s="5">
-        <v>0</v>
-      </c>
-      <c r="L701" s="5">
-        <v>61</v>
-      </c>
-      <c r="M701" s="5"/>
-      <c r="N701" s="5"/>
-      <c r="O701" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A702" s="5"/>
-      <c r="K702" s="5">
-        <v>0</v>
-      </c>
-      <c r="L702" s="5">
-        <v>61</v>
-      </c>
-      <c r="M702" s="5"/>
-      <c r="N702" s="5"/>
-      <c r="O702" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A703" s="5"/>
-      <c r="K703" s="5">
-        <v>0</v>
-      </c>
-      <c r="L703" s="5">
-        <v>61</v>
-      </c>
-      <c r="M703" s="5"/>
-      <c r="N703" s="5"/>
-      <c r="O703" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A704" s="5"/>
-      <c r="K704" s="5">
-        <v>0</v>
-      </c>
-      <c r="L704" s="5">
-        <v>61</v>
-      </c>
-      <c r="M704" s="5"/>
-      <c r="N704" s="5"/>
-      <c r="O704" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A705" s="5"/>
-      <c r="K705" s="5">
-        <v>0</v>
-      </c>
-      <c r="L705" s="5">
-        <v>61</v>
-      </c>
-      <c r="M705" s="5"/>
-      <c r="N705" s="5"/>
-      <c r="O705" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A706" s="5"/>
-      <c r="K706" s="5">
-        <v>0</v>
-      </c>
-      <c r="L706" s="5">
-        <v>61</v>
-      </c>
-      <c r="M706" s="5"/>
-      <c r="N706" s="5"/>
-      <c r="O706" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A707" s="5"/>
-      <c r="K707" s="5">
-        <v>0</v>
-      </c>
-      <c r="L707" s="5">
-        <v>61</v>
-      </c>
-      <c r="M707" s="5"/>
-      <c r="N707" s="5"/>
-      <c r="O707" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A708" s="5"/>
-      <c r="K708" s="5">
-        <v>0</v>
-      </c>
-      <c r="L708" s="5">
-        <v>61</v>
-      </c>
-      <c r="M708" s="5"/>
-      <c r="N708" s="5"/>
-      <c r="O708" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A709" s="5"/>
-      <c r="K709" s="5">
-        <v>0</v>
-      </c>
-      <c r="L709" s="5">
-        <v>61</v>
-      </c>
-      <c r="M709" s="5"/>
-      <c r="N709" s="5"/>
-      <c r="O709" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A710" s="5"/>
-      <c r="K710" s="5">
-        <v>0</v>
-      </c>
-      <c r="L710" s="5">
-        <v>61</v>
-      </c>
-      <c r="M710" s="5"/>
-      <c r="N710" s="5"/>
-      <c r="O710" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A711" s="5"/>
-      <c r="K711" s="5">
-        <v>0</v>
-      </c>
-      <c r="L711" s="5">
-        <v>61</v>
-      </c>
-      <c r="M711" s="5"/>
-      <c r="N711" s="5"/>
-      <c r="O711" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A712" s="5"/>
-      <c r="K712" s="5">
-        <v>0</v>
-      </c>
-      <c r="L712" s="5">
-        <v>61</v>
-      </c>
-      <c r="M712" s="5"/>
-      <c r="N712" s="5"/>
-      <c r="O712" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A713" s="5"/>
-      <c r="K713" s="5">
-        <v>0</v>
-      </c>
-      <c r="L713" s="5">
-        <v>61</v>
-      </c>
-      <c r="M713" s="5"/>
-      <c r="N713" s="5"/>
-      <c r="O713" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A714" s="5"/>
-      <c r="K714" s="5">
-        <v>0</v>
-      </c>
-      <c r="L714" s="5">
-        <v>61</v>
-      </c>
-      <c r="M714" s="5"/>
-      <c r="N714" s="5"/>
-      <c r="O714" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A715" s="5"/>
-      <c r="K715" s="5">
-        <v>0</v>
-      </c>
-      <c r="L715" s="5">
-        <v>61</v>
-      </c>
-      <c r="M715" s="5"/>
-      <c r="N715" s="5"/>
-      <c r="O715" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A716" s="5"/>
-      <c r="K716" s="5">
-        <v>0</v>
-      </c>
-      <c r="L716" s="5">
-        <v>61</v>
-      </c>
-      <c r="M716" s="5"/>
-      <c r="N716" s="5"/>
-      <c r="O716" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A717" s="5"/>
-      <c r="K717" s="5">
-        <v>0</v>
-      </c>
-      <c r="L717" s="5">
-        <v>61</v>
-      </c>
-      <c r="M717" s="5"/>
-      <c r="N717" s="5"/>
-      <c r="O717" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A718" s="5"/>
-      <c r="K718" s="5">
-        <v>0</v>
-      </c>
-      <c r="L718" s="5">
-        <v>61</v>
-      </c>
-      <c r="M718" s="5"/>
-      <c r="N718" s="5"/>
-      <c r="O718" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A719" s="5"/>
-      <c r="K719" s="5">
-        <v>0</v>
-      </c>
-      <c r="L719" s="5">
-        <v>61</v>
-      </c>
-      <c r="M719" s="5"/>
-      <c r="N719" s="5"/>
-      <c r="O719" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A720" s="5"/>
-      <c r="K720" s="5">
-        <v>0</v>
-      </c>
-      <c r="L720" s="5">
-        <v>61</v>
-      </c>
-      <c r="M720" s="5"/>
-      <c r="N720" s="5"/>
-      <c r="O720" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A721" s="5"/>
-      <c r="K721" s="5">
-        <v>0</v>
-      </c>
-      <c r="L721" s="5">
-        <v>61</v>
-      </c>
-      <c r="M721" s="5"/>
-      <c r="N721" s="5"/>
-      <c r="O721" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A722" s="5"/>
-      <c r="K722" s="5">
-        <v>0</v>
-      </c>
-      <c r="L722" s="5">
-        <v>61</v>
-      </c>
-      <c r="M722" s="5"/>
-      <c r="N722" s="5"/>
-      <c r="O722" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A723" s="5"/>
-      <c r="K723" s="5">
-        <v>0</v>
-      </c>
-      <c r="L723" s="5">
-        <v>61</v>
-      </c>
-      <c r="M723" s="5"/>
-      <c r="N723" s="5"/>
-      <c r="O723" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A724" s="5"/>
-      <c r="K724" s="5">
-        <v>0</v>
-      </c>
-      <c r="L724" s="5">
-        <v>61</v>
-      </c>
-      <c r="M724" s="5"/>
-      <c r="N724" s="5"/>
-      <c r="O724" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A725" s="5"/>
-      <c r="K725" s="5">
-        <v>0</v>
-      </c>
-      <c r="L725" s="5">
-        <v>61</v>
-      </c>
-      <c r="M725" s="5"/>
-      <c r="N725" s="5"/>
-      <c r="O725" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A726" s="5"/>
-      <c r="K726" s="5">
-        <v>0</v>
-      </c>
-      <c r="L726" s="5">
-        <v>61</v>
-      </c>
-      <c r="M726" s="5"/>
-      <c r="N726" s="5"/>
-      <c r="O726" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A727" s="5"/>
-      <c r="K727" s="5">
-        <v>0</v>
-      </c>
-      <c r="L727" s="5">
-        <v>61</v>
-      </c>
-      <c r="M727" s="5"/>
-      <c r="N727" s="5"/>
-      <c r="O727" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A728" s="5"/>
-      <c r="K728" s="5">
-        <v>0</v>
-      </c>
-      <c r="L728" s="5">
-        <v>61</v>
-      </c>
-      <c r="M728" s="5"/>
-      <c r="N728" s="5"/>
-      <c r="O728" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A729" s="5"/>
-      <c r="K729" s="5">
-        <v>0</v>
-      </c>
-      <c r="L729" s="5">
-        <v>61</v>
-      </c>
-      <c r="M729" s="5"/>
-      <c r="N729" s="5"/>
-      <c r="O729" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A730" s="5"/>
-      <c r="K730" s="5">
-        <v>0</v>
-      </c>
-      <c r="L730" s="5">
-        <v>61</v>
-      </c>
-      <c r="M730" s="5"/>
-      <c r="N730" s="5"/>
-      <c r="O730" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A731" s="5"/>
-      <c r="K731" s="5">
-        <v>0</v>
-      </c>
-      <c r="L731" s="5">
-        <v>61</v>
-      </c>
-      <c r="M731" s="5"/>
-      <c r="N731" s="5"/>
-      <c r="O731" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A732" s="5"/>
-      <c r="K732" s="5">
-        <v>0</v>
-      </c>
-      <c r="L732" s="5">
-        <v>61</v>
-      </c>
-      <c r="M732" s="5"/>
-      <c r="N732" s="5"/>
-      <c r="O732" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A733" s="5"/>
-      <c r="K733" s="5">
-        <v>0</v>
-      </c>
-      <c r="L733" s="5">
-        <v>61</v>
-      </c>
-      <c r="M733" s="5"/>
-      <c r="N733" s="5"/>
-      <c r="O733" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A734" s="5"/>
-      <c r="K734" s="5">
-        <v>0</v>
-      </c>
-      <c r="L734" s="5">
-        <v>61</v>
-      </c>
-      <c r="M734" s="5"/>
-      <c r="N734" s="5"/>
-      <c r="O734" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A735" s="5"/>
-      <c r="K735" s="5">
-        <v>0</v>
-      </c>
-      <c r="L735" s="5">
-        <v>61</v>
-      </c>
-      <c r="M735" s="5"/>
-      <c r="N735" s="5"/>
-      <c r="O735" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A736" s="5"/>
-      <c r="K736" s="5">
-        <v>0</v>
-      </c>
-      <c r="L736" s="5">
-        <v>61</v>
-      </c>
-      <c r="M736" s="5"/>
-      <c r="N736" s="5"/>
-      <c r="O736" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A737" s="5"/>
-      <c r="K737" s="5">
-        <v>0</v>
-      </c>
-      <c r="L737" s="5">
-        <v>61</v>
-      </c>
-      <c r="M737" s="5"/>
-      <c r="N737" s="5"/>
-      <c r="O737" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A738" s="5"/>
-      <c r="K738" s="5">
-        <v>0</v>
-      </c>
-      <c r="L738" s="5">
-        <v>61</v>
-      </c>
-      <c r="M738" s="5"/>
-      <c r="N738" s="5"/>
-      <c r="O738" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A739" s="5"/>
-      <c r="K739" s="5">
-        <v>0</v>
-      </c>
-      <c r="L739" s="5">
-        <v>61</v>
-      </c>
-      <c r="M739" s="5"/>
-      <c r="N739" s="5"/>
-      <c r="O739" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A740" s="5"/>
-      <c r="K740" s="5">
-        <v>0</v>
-      </c>
-      <c r="L740" s="5">
-        <v>61</v>
-      </c>
-      <c r="M740" s="5"/>
-      <c r="N740" s="5"/>
-      <c r="O740" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A741" s="5"/>
-      <c r="K741" s="5">
-        <v>0</v>
-      </c>
-      <c r="L741" s="5">
-        <v>61</v>
-      </c>
-      <c r="M741" s="5"/>
-      <c r="N741" s="5"/>
-      <c r="O741" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A742" s="5"/>
-      <c r="K742" s="5">
-        <v>0</v>
-      </c>
-      <c r="L742" s="5">
-        <v>61</v>
-      </c>
-      <c r="M742" s="5"/>
-      <c r="N742" s="5"/>
-      <c r="O742" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A743" s="5"/>
-      <c r="K743" s="5">
-        <v>0</v>
-      </c>
-      <c r="L743" s="5">
-        <v>61</v>
-      </c>
-      <c r="M743" s="5"/>
-      <c r="N743" s="5"/>
-      <c r="O743" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A744" s="5"/>
-      <c r="K744" s="5">
-        <v>0</v>
-      </c>
-      <c r="L744" s="5">
-        <v>61</v>
-      </c>
-      <c r="M744" s="5"/>
-      <c r="N744" s="5"/>
-      <c r="O744" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A745" s="5"/>
-      <c r="K745" s="5">
-        <v>0</v>
-      </c>
-      <c r="L745" s="5">
-        <v>61</v>
-      </c>
-      <c r="M745" s="5"/>
-      <c r="N745" s="5"/>
-      <c r="O745" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A746" s="5"/>
-      <c r="K746" s="5">
-        <v>0</v>
-      </c>
-      <c r="L746" s="5">
-        <v>61</v>
-      </c>
-      <c r="M746" s="5"/>
-      <c r="N746" s="5"/>
-      <c r="O746" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A747" s="5"/>
-      <c r="K747" s="5">
-        <v>0</v>
-      </c>
-      <c r="L747" s="5">
-        <v>61</v>
-      </c>
-      <c r="M747" s="5"/>
-      <c r="N747" s="5"/>
-      <c r="O747" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A748" s="5"/>
-      <c r="K748" s="5">
-        <v>0</v>
-      </c>
-      <c r="L748" s="5">
-        <v>61</v>
-      </c>
-      <c r="M748" s="5"/>
-      <c r="N748" s="5"/>
-      <c r="O748" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A749" s="5"/>
-      <c r="K749" s="5">
-        <v>0</v>
-      </c>
-      <c r="L749" s="5">
-        <v>61</v>
-      </c>
-      <c r="M749" s="5"/>
-      <c r="N749" s="5"/>
-      <c r="O749" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A750" s="5"/>
-      <c r="K750" s="5">
-        <v>0</v>
-      </c>
-      <c r="L750" s="5">
-        <v>61</v>
-      </c>
-      <c r="M750" s="5"/>
-      <c r="N750" s="5"/>
-      <c r="O750" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A751" s="5"/>
-      <c r="K751" s="5">
-        <v>0</v>
-      </c>
-      <c r="L751" s="5">
-        <v>61</v>
-      </c>
-      <c r="M751" s="5"/>
-      <c r="N751" s="5"/>
-      <c r="O751" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A752" s="5"/>
-      <c r="K752" s="5">
-        <v>0</v>
-      </c>
-      <c r="L752" s="5">
-        <v>61</v>
-      </c>
-      <c r="M752" s="5"/>
-      <c r="N752" s="5"/>
-      <c r="O752" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A753" s="5"/>
-      <c r="K753" s="5">
-        <v>0</v>
-      </c>
-      <c r="L753" s="5">
-        <v>61</v>
-      </c>
-      <c r="M753" s="5"/>
-      <c r="N753" s="5"/>
-      <c r="O753" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A754" s="5"/>
-      <c r="K754" s="5">
-        <v>0</v>
-      </c>
-      <c r="L754" s="5">
-        <v>61</v>
-      </c>
-      <c r="M754" s="5"/>
-      <c r="N754" s="5"/>
-      <c r="O754" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A755" s="5"/>
-      <c r="K755" s="5">
-        <v>0</v>
-      </c>
-      <c r="L755" s="5">
-        <v>61</v>
-      </c>
-      <c r="M755" s="5"/>
-      <c r="N755" s="5"/>
-      <c r="O755" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A756" s="5"/>
-      <c r="K756" s="5">
-        <v>0</v>
-      </c>
-      <c r="L756" s="5">
-        <v>61</v>
-      </c>
-      <c r="M756" s="5"/>
-      <c r="N756" s="5"/>
-      <c r="O756" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A757" s="5"/>
-      <c r="K757" s="5">
-        <v>0</v>
-      </c>
-      <c r="L757" s="5">
-        <v>61</v>
-      </c>
-      <c r="M757" s="5"/>
-      <c r="N757" s="5"/>
-      <c r="O757" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A758" s="5"/>
-      <c r="K758" s="5">
-        <v>0</v>
-      </c>
-      <c r="L758" s="5">
-        <v>61</v>
-      </c>
-      <c r="M758" s="5"/>
-      <c r="N758" s="5"/>
-      <c r="O758" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A759" s="5"/>
-      <c r="K759" s="5">
-        <v>0</v>
-      </c>
-      <c r="L759" s="5">
-        <v>61</v>
-      </c>
-      <c r="M759" s="5"/>
-      <c r="N759" s="5"/>
-      <c r="O759" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A760" s="5"/>
-      <c r="K760" s="5">
-        <v>0</v>
-      </c>
-      <c r="L760" s="5">
-        <v>61</v>
-      </c>
-      <c r="M760" s="5"/>
-      <c r="N760" s="5"/>
-      <c r="O760" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A761" s="5"/>
-      <c r="K761" s="5">
-        <v>0</v>
-      </c>
-      <c r="L761" s="5">
-        <v>61</v>
-      </c>
-      <c r="M761" s="5"/>
-      <c r="N761" s="5"/>
-      <c r="O761" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A762" s="5"/>
-      <c r="K762" s="5">
-        <v>0</v>
-      </c>
-      <c r="L762" s="5">
-        <v>61</v>
-      </c>
-      <c r="M762" s="5"/>
-      <c r="N762" s="5"/>
-      <c r="O762" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A763" s="5"/>
-      <c r="K763" s="5">
-        <v>0</v>
-      </c>
-      <c r="L763" s="5">
-        <v>61</v>
-      </c>
-      <c r="M763" s="5"/>
-      <c r="N763" s="5"/>
-      <c r="O763" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A764" s="5"/>
-      <c r="K764" s="5">
-        <v>0</v>
-      </c>
-      <c r="L764" s="5">
-        <v>61</v>
-      </c>
-      <c r="M764" s="5"/>
-      <c r="N764" s="5"/>
-      <c r="O764" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A765" s="5"/>
-      <c r="K765" s="5">
-        <v>0</v>
-      </c>
-      <c r="L765" s="5">
-        <v>61</v>
-      </c>
-      <c r="M765" s="5"/>
-      <c r="N765" s="5"/>
-      <c r="O765" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A766" s="5"/>
-      <c r="K766" s="5">
-        <v>0</v>
-      </c>
-      <c r="L766" s="5">
-        <v>61</v>
-      </c>
-      <c r="M766" s="5"/>
-      <c r="N766" s="5"/>
-      <c r="O766" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A767" s="5"/>
-      <c r="K767" s="5">
-        <v>0</v>
-      </c>
-      <c r="L767" s="5">
-        <v>61</v>
-      </c>
-      <c r="M767" s="5"/>
-      <c r="N767" s="5"/>
-      <c r="O767" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A768" s="5"/>
-      <c r="K768" s="5">
-        <v>0</v>
-      </c>
-      <c r="L768" s="5">
-        <v>61</v>
-      </c>
-      <c r="M768" s="5"/>
-      <c r="N768" s="5"/>
-      <c r="O768" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A769" s="5"/>
-      <c r="K769" s="5">
-        <v>0</v>
-      </c>
-      <c r="L769" s="5">
-        <v>61</v>
-      </c>
-      <c r="M769" s="5"/>
-      <c r="N769" s="5"/>
-      <c r="O769" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A770" s="5"/>
-      <c r="K770" s="5">
-        <v>0</v>
-      </c>
-      <c r="L770" s="5">
-        <v>61</v>
-      </c>
-      <c r="M770" s="5"/>
-      <c r="N770" s="5"/>
-      <c r="O770" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A771" s="5"/>
-      <c r="K771" s="5">
-        <v>0</v>
-      </c>
-      <c r="L771" s="5">
-        <v>61</v>
-      </c>
-      <c r="M771" s="5"/>
-      <c r="N771" s="5"/>
-      <c r="O771" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A772" s="5"/>
-      <c r="K772" s="5">
-        <v>0</v>
-      </c>
-      <c r="L772" s="5">
-        <v>61</v>
-      </c>
-      <c r="M772" s="5"/>
-      <c r="N772" s="5"/>
-      <c r="O772" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A773" s="5"/>
-      <c r="K773" s="5">
-        <v>0</v>
-      </c>
-      <c r="L773" s="5">
-        <v>61</v>
-      </c>
-      <c r="M773" s="5"/>
-      <c r="N773" s="5"/>
-      <c r="O773" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A774" s="5"/>
-      <c r="K774" s="5">
-        <v>0</v>
-      </c>
-      <c r="L774" s="5">
-        <v>61</v>
-      </c>
-      <c r="M774" s="5"/>
-      <c r="N774" s="5"/>
-      <c r="O774" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A775" s="5"/>
-      <c r="K775" s="5">
-        <v>0</v>
-      </c>
-      <c r="L775" s="5">
-        <v>61</v>
-      </c>
-      <c r="M775" s="5"/>
-      <c r="N775" s="5"/>
-      <c r="O775" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A776" s="5"/>
-      <c r="K776" s="5">
-        <v>0</v>
-      </c>
-      <c r="L776" s="5">
-        <v>61</v>
-      </c>
-      <c r="M776" s="5"/>
-      <c r="N776" s="5"/>
-      <c r="O776" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A777" s="5"/>
-      <c r="K777" s="5">
-        <v>0</v>
-      </c>
-      <c r="L777" s="5">
-        <v>61</v>
-      </c>
-      <c r="M777" s="5"/>
-      <c r="N777" s="5"/>
-      <c r="O777" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A778" s="5"/>
-      <c r="K778" s="5">
-        <v>0</v>
-      </c>
-      <c r="L778" s="5">
-        <v>61</v>
-      </c>
-      <c r="M778" s="5"/>
-      <c r="N778" s="5"/>
-      <c r="O778" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A779" s="5"/>
-      <c r="K779" s="5">
-        <v>0</v>
-      </c>
-      <c r="L779" s="5">
-        <v>61</v>
-      </c>
-      <c r="M779" s="5"/>
-      <c r="N779" s="5"/>
-      <c r="O779" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A780" s="5"/>
-      <c r="K780" s="5">
-        <v>0</v>
-      </c>
-      <c r="L780" s="5">
-        <v>61</v>
-      </c>
-      <c r="M780" s="5"/>
-      <c r="N780" s="5"/>
-      <c r="O780" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A781" s="5"/>
-      <c r="K781" s="5">
-        <v>0</v>
-      </c>
-      <c r="L781" s="5">
-        <v>61</v>
-      </c>
-      <c r="M781" s="5"/>
-      <c r="N781" s="5"/>
-      <c r="O781" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A782" s="5"/>
-      <c r="K782" s="5">
-        <v>0</v>
-      </c>
-      <c r="L782" s="5">
-        <v>61</v>
-      </c>
-      <c r="M782" s="5"/>
-      <c r="N782" s="5"/>
-      <c r="O782" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A783" s="5"/>
-      <c r="K783" s="5">
-        <v>0</v>
-      </c>
-      <c r="L783" s="5">
-        <v>61</v>
-      </c>
-      <c r="M783" s="5"/>
-      <c r="N783" s="5"/>
-      <c r="O783" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A784" s="5"/>
-      <c r="K784" s="5">
-        <v>0</v>
-      </c>
-      <c r="L784" s="5">
-        <v>61</v>
-      </c>
-      <c r="M784" s="5"/>
-      <c r="N784" s="5"/>
-      <c r="O784" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A785" s="5"/>
-      <c r="K785" s="5">
-        <v>0</v>
-      </c>
-      <c r="L785" s="5">
-        <v>61</v>
-      </c>
-      <c r="M785" s="5"/>
-      <c r="N785" s="5"/>
-      <c r="O785" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A786" s="5"/>
-      <c r="K786" s="5">
-        <v>0</v>
-      </c>
-      <c r="L786" s="5">
-        <v>61</v>
-      </c>
-      <c r="M786" s="5"/>
-      <c r="N786" s="5"/>
-      <c r="O786" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A787" s="5"/>
-      <c r="K787" s="5">
-        <v>0</v>
-      </c>
-      <c r="L787" s="5">
-        <v>61</v>
-      </c>
-      <c r="M787" s="5"/>
-      <c r="N787" s="5"/>
-      <c r="O787" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A788" s="5"/>
-      <c r="K788" s="5">
-        <v>0</v>
-      </c>
-      <c r="L788" s="5">
-        <v>61</v>
-      </c>
-      <c r="M788" s="5"/>
-      <c r="N788" s="5"/>
-      <c r="O788" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A789" s="5"/>
-      <c r="K789" s="5">
-        <v>0</v>
-      </c>
-      <c r="L789" s="5">
-        <v>61</v>
-      </c>
-      <c r="M789" s="5"/>
-      <c r="N789" s="5"/>
-      <c r="O789" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A790" s="5"/>
-      <c r="K790" s="5">
-        <v>0</v>
-      </c>
-      <c r="L790" s="5">
-        <v>61</v>
-      </c>
-      <c r="M790" s="5"/>
-      <c r="N790" s="5"/>
-      <c r="O790" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A791" s="5"/>
-      <c r="K791" s="5">
-        <v>0</v>
-      </c>
-      <c r="L791" s="5">
-        <v>61</v>
-      </c>
-      <c r="M791" s="5"/>
-      <c r="N791" s="5"/>
-      <c r="O791" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A792" s="5"/>
-      <c r="K792" s="5">
-        <v>0</v>
-      </c>
-      <c r="L792" s="5">
-        <v>61</v>
-      </c>
-      <c r="M792" s="5"/>
-      <c r="N792" s="5"/>
-      <c r="O792" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A793" s="5"/>
-      <c r="K793" s="5">
-        <v>0</v>
-      </c>
-      <c r="L793" s="5">
-        <v>61</v>
-      </c>
-      <c r="M793" s="5"/>
-      <c r="N793" s="5"/>
-      <c r="O793" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A794" s="5"/>
-      <c r="K794" s="5">
-        <v>0</v>
-      </c>
-      <c r="L794" s="5">
-        <v>61</v>
-      </c>
-      <c r="M794" s="5"/>
-      <c r="N794" s="5"/>
-      <c r="O794" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A795" s="5"/>
-      <c r="K795" s="5">
-        <v>0</v>
-      </c>
-      <c r="L795" s="5">
-        <v>61</v>
-      </c>
-      <c r="M795" s="5"/>
-      <c r="N795" s="5"/>
-      <c r="O795" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A796" s="5"/>
-      <c r="K796" s="5">
-        <v>0</v>
-      </c>
-      <c r="L796" s="5">
-        <v>61</v>
-      </c>
-      <c r="M796" s="5"/>
-      <c r="N796" s="5"/>
-      <c r="O796" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A797" s="5"/>
-      <c r="K797" s="5">
-        <v>0</v>
-      </c>
-      <c r="L797" s="5">
-        <v>61</v>
-      </c>
-      <c r="M797" s="5"/>
-      <c r="N797" s="5"/>
-      <c r="O797" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A798" s="5"/>
-      <c r="K798" s="5">
-        <v>0</v>
-      </c>
-      <c r="L798" s="5">
-        <v>61</v>
-      </c>
-      <c r="M798" s="5"/>
-      <c r="N798" s="5"/>
-      <c r="O798" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A799" s="5"/>
-      <c r="K799" s="5">
-        <v>0</v>
-      </c>
-      <c r="L799" s="5">
-        <v>61</v>
-      </c>
-      <c r="M799" s="5"/>
-      <c r="N799" s="5"/>
-      <c r="O799" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A800" s="5"/>
-      <c r="K800" s="5">
-        <v>0</v>
-      </c>
-      <c r="L800" s="5">
-        <v>61</v>
-      </c>
-      <c r="M800" s="5"/>
-      <c r="N800" s="5"/>
-      <c r="O800" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A801" s="5"/>
-      <c r="K801" s="5">
-        <v>0</v>
-      </c>
-      <c r="L801" s="5">
-        <v>61</v>
-      </c>
-      <c r="M801" s="5"/>
-      <c r="N801" s="5"/>
-      <c r="O801" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A802" s="5"/>
-      <c r="K802" s="5">
-        <v>0</v>
-      </c>
-      <c r="L802" s="5">
-        <v>61</v>
-      </c>
-      <c r="M802" s="5"/>
-      <c r="N802" s="5"/>
-      <c r="O802" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A803" s="5"/>
-      <c r="K803" s="5">
-        <v>0</v>
-      </c>
-      <c r="L803" s="5">
-        <v>61</v>
-      </c>
-      <c r="M803" s="5"/>
-      <c r="N803" s="5"/>
-      <c r="O803" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A804" s="5"/>
-      <c r="K804" s="5">
-        <v>0</v>
-      </c>
-      <c r="L804" s="5">
-        <v>61</v>
-      </c>
-      <c r="M804" s="5"/>
-      <c r="N804" s="5"/>
-      <c r="O804" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A805" s="5"/>
-      <c r="K805" s="5">
-        <v>0</v>
-      </c>
-      <c r="L805" s="5">
-        <v>61</v>
-      </c>
-      <c r="M805" s="5"/>
-      <c r="N805" s="5"/>
-      <c r="O805" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A806" s="5"/>
-      <c r="K806" s="5">
-        <v>0</v>
-      </c>
-      <c r="L806" s="5">
-        <v>61</v>
-      </c>
-      <c r="M806" s="5"/>
-      <c r="N806" s="5"/>
-      <c r="O806" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A807" s="5"/>
-      <c r="K807" s="5">
-        <v>0</v>
-      </c>
-      <c r="L807" s="5">
-        <v>61</v>
-      </c>
-      <c r="M807" s="5"/>
-      <c r="N807" s="5"/>
-      <c r="O807" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A808" s="5"/>
-      <c r="K808" s="5">
-        <v>0</v>
-      </c>
-      <c r="L808" s="5">
-        <v>61</v>
-      </c>
-      <c r="M808" s="5"/>
-      <c r="N808" s="5"/>
-      <c r="O808" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A809" s="5"/>
-      <c r="K809" s="5">
-        <v>0</v>
-      </c>
-      <c r="L809" s="5">
-        <v>61</v>
-      </c>
-      <c r="M809" s="5"/>
-      <c r="N809" s="5"/>
-      <c r="O809" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A810" s="5"/>
-      <c r="K810" s="5">
-        <v>0</v>
-      </c>
-      <c r="L810" s="5">
-        <v>61</v>
-      </c>
-      <c r="M810" s="5"/>
-      <c r="N810" s="5"/>
-      <c r="O810" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A811" s="5"/>
-      <c r="K811" s="5">
-        <v>0</v>
-      </c>
-      <c r="L811" s="5">
-        <v>61</v>
-      </c>
-      <c r="M811" s="5"/>
-      <c r="N811" s="5"/>
-      <c r="O811" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A812" s="5"/>
-      <c r="K812" s="5">
-        <v>0</v>
-      </c>
-      <c r="L812" s="5">
-        <v>61</v>
-      </c>
-      <c r="M812" s="5"/>
-      <c r="N812" s="5"/>
-      <c r="O812" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A813" s="5"/>
-      <c r="K813" s="5">
-        <v>0</v>
-      </c>
-      <c r="L813" s="5">
-        <v>61</v>
-      </c>
-      <c r="M813" s="5"/>
-      <c r="N813" s="5"/>
-      <c r="O813" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A814" s="5"/>
-      <c r="K814" s="5">
-        <v>0</v>
-      </c>
-      <c r="L814" s="5">
-        <v>61</v>
-      </c>
-      <c r="M814" s="5"/>
-      <c r="N814" s="5"/>
-      <c r="O814" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A815" s="5"/>
-      <c r="K815" s="5">
-        <v>0</v>
-      </c>
-      <c r="L815" s="5">
-        <v>61</v>
-      </c>
-      <c r="M815" s="5"/>
-      <c r="N815" s="5"/>
-      <c r="O815" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A816" s="5"/>
-      <c r="K816" s="5">
-        <v>0</v>
-      </c>
-      <c r="L816" s="5">
-        <v>61</v>
-      </c>
-      <c r="M816" s="5"/>
-      <c r="N816" s="5"/>
-      <c r="O816" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A817" s="5"/>
-      <c r="K817" s="5">
-        <v>0</v>
-      </c>
-      <c r="L817" s="5">
-        <v>61</v>
-      </c>
-      <c r="M817" s="5"/>
-      <c r="N817" s="5"/>
-      <c r="O817" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A818" s="5"/>
-      <c r="K818" s="5">
-        <v>0</v>
-      </c>
-      <c r="L818" s="5">
-        <v>61</v>
-      </c>
-      <c r="M818" s="5"/>
-      <c r="N818" s="5"/>
-      <c r="O818" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A819" s="5"/>
-      <c r="K819" s="5">
-        <v>0</v>
-      </c>
-      <c r="L819" s="5">
-        <v>61</v>
-      </c>
-      <c r="M819" s="5"/>
-      <c r="N819" s="5"/>
-      <c r="O819" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A820" s="5"/>
-      <c r="K820" s="5">
-        <v>0</v>
-      </c>
-      <c r="L820" s="5">
-        <v>61</v>
-      </c>
-      <c r="M820" s="5"/>
-      <c r="N820" s="5"/>
-      <c r="O820" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A821" s="5"/>
-      <c r="K821" s="5">
-        <v>0</v>
-      </c>
-      <c r="L821" s="5">
-        <v>61</v>
-      </c>
-      <c r="M821" s="5"/>
-      <c r="N821" s="5"/>
-      <c r="O821" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A822" s="5"/>
-      <c r="K822" s="5">
-        <v>0</v>
-      </c>
-      <c r="L822" s="5">
-        <v>61</v>
-      </c>
-      <c r="M822" s="5"/>
-      <c r="N822" s="5"/>
-      <c r="O822" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A823" s="5"/>
-      <c r="K823" s="5">
-        <v>0</v>
-      </c>
-      <c r="L823" s="5">
-        <v>61</v>
-      </c>
-      <c r="M823" s="5"/>
-      <c r="N823" s="5"/>
-      <c r="O823" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A824" s="5"/>
-      <c r="K824" s="5">
-        <v>0</v>
-      </c>
-      <c r="L824" s="5">
-        <v>61</v>
-      </c>
-      <c r="M824" s="5"/>
-      <c r="N824" s="5"/>
-      <c r="O824" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A825" s="5"/>
-      <c r="K825" s="5">
-        <v>0</v>
-      </c>
-      <c r="L825" s="5">
-        <v>61</v>
-      </c>
-      <c r="M825" s="5"/>
-      <c r="N825" s="5"/>
-      <c r="O825" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A826" s="5"/>
-      <c r="K826" s="5">
-        <v>0</v>
-      </c>
-      <c r="L826" s="5">
-        <v>61</v>
-      </c>
-      <c r="M826" s="5"/>
-      <c r="N826" s="5"/>
-      <c r="O826" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A827" s="5"/>
-      <c r="K827" s="5">
-        <v>0</v>
-      </c>
-      <c r="L827" s="5">
-        <v>61</v>
-      </c>
-      <c r="M827" s="5"/>
-      <c r="N827" s="5"/>
-      <c r="O827" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A828" s="5"/>
-      <c r="K828" s="5">
-        <v>0</v>
-      </c>
-      <c r="L828" s="5">
-        <v>61</v>
-      </c>
-      <c r="M828" s="5"/>
-      <c r="N828" s="5"/>
-      <c r="O828" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A829" s="5"/>
-      <c r="K829" s="5">
-        <v>0</v>
-      </c>
-      <c r="L829" s="5">
-        <v>61</v>
-      </c>
-      <c r="M829" s="5"/>
-      <c r="N829" s="5"/>
-      <c r="O829" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A830" s="5"/>
-      <c r="K830" s="5">
-        <v>0</v>
-      </c>
-      <c r="L830" s="5">
-        <v>61</v>
-      </c>
-      <c r="M830" s="5"/>
-      <c r="N830" s="5"/>
-      <c r="O830" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A831" s="5"/>
-      <c r="K831" s="5">
-        <v>0</v>
-      </c>
-      <c r="L831" s="5">
-        <v>61</v>
-      </c>
-      <c r="M831" s="5"/>
-      <c r="N831" s="5"/>
-      <c r="O831" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A832" s="5"/>
-      <c r="K832" s="5">
-        <v>0</v>
-      </c>
-      <c r="L832" s="5">
-        <v>61</v>
-      </c>
-      <c r="M832" s="5"/>
-      <c r="N832" s="5"/>
-      <c r="O832" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A833" s="5"/>
-      <c r="K833" s="5">
-        <v>0</v>
-      </c>
-      <c r="L833" s="5">
-        <v>61</v>
-      </c>
-      <c r="M833" s="5"/>
-      <c r="N833" s="5"/>
-      <c r="O833" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A834" s="5"/>
-      <c r="K834" s="5">
-        <v>0</v>
-      </c>
-      <c r="L834" s="5">
-        <v>61</v>
-      </c>
-      <c r="M834" s="5"/>
-      <c r="N834" s="5"/>
-      <c r="O834" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A835" s="5"/>
-      <c r="K835" s="5">
-        <v>0</v>
-      </c>
-      <c r="L835" s="5">
-        <v>61</v>
-      </c>
-      <c r="M835" s="5"/>
-      <c r="N835" s="5"/>
-      <c r="O835" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A836" s="5"/>
-      <c r="K836" s="5">
-        <v>0</v>
-      </c>
-      <c r="L836" s="5">
-        <v>61</v>
-      </c>
-      <c r="M836" s="5"/>
-      <c r="N836" s="5"/>
-      <c r="O836" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A837" s="5"/>
-      <c r="K837" s="5">
-        <v>0</v>
-      </c>
-      <c r="L837" s="5">
-        <v>61</v>
-      </c>
-      <c r="M837" s="5"/>
-      <c r="N837" s="5"/>
-      <c r="O837" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A838" s="5"/>
-      <c r="K838" s="5">
-        <v>0</v>
-      </c>
-      <c r="L838" s="5">
-        <v>61</v>
-      </c>
-      <c r="M838" s="5"/>
-      <c r="N838" s="5"/>
-      <c r="O838" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A839" s="5"/>
-      <c r="K839" s="5">
-        <v>0</v>
-      </c>
-      <c r="L839" s="5">
-        <v>61</v>
-      </c>
-      <c r="M839" s="5"/>
-      <c r="N839" s="5"/>
-      <c r="O839" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A840" s="5"/>
-      <c r="K840" s="5">
-        <v>0</v>
-      </c>
-      <c r="L840" s="5">
-        <v>61</v>
-      </c>
-      <c r="M840" s="5"/>
-      <c r="N840" s="5"/>
-      <c r="O840" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="841" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A841" s="5"/>
-      <c r="K841" s="5">
-        <v>0</v>
-      </c>
-      <c r="L841" s="5">
-        <v>61</v>
-      </c>
-      <c r="M841" s="5"/>
-      <c r="N841" s="5"/>
-      <c r="O841" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="842" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A842" s="5"/>
-      <c r="K842" s="5">
-        <v>0</v>
-      </c>
-      <c r="L842" s="5">
-        <v>61</v>
-      </c>
-      <c r="M842" s="5"/>
-      <c r="N842" s="5"/>
-      <c r="O842" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="843" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A843" s="5"/>
-      <c r="K843" s="5">
-        <v>0</v>
-      </c>
-      <c r="L843" s="5">
-        <v>61</v>
-      </c>
-      <c r="M843" s="5"/>
-      <c r="N843" s="5"/>
-      <c r="O843" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="844" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A844" s="5"/>
-      <c r="K844" s="5">
-        <v>0</v>
-      </c>
-      <c r="L844" s="5">
-        <v>61</v>
-      </c>
-      <c r="M844" s="5"/>
-      <c r="N844" s="5"/>
-      <c r="O844" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A845" s="5"/>
-      <c r="K845" s="5">
-        <v>0</v>
-      </c>
-      <c r="L845" s="5">
-        <v>61</v>
-      </c>
-      <c r="M845" s="5"/>
-      <c r="N845" s="5"/>
-      <c r="O845" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A846" s="5"/>
-      <c r="K846" s="5">
-        <v>0</v>
-      </c>
-      <c r="L846" s="5">
-        <v>61</v>
-      </c>
-      <c r="M846" s="5"/>
-      <c r="N846" s="5"/>
-      <c r="O846" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A847" s="5"/>
-      <c r="K847" s="5">
-        <v>0</v>
-      </c>
-      <c r="L847" s="5">
-        <v>61</v>
-      </c>
-      <c r="M847" s="5"/>
-      <c r="N847" s="5"/>
-      <c r="O847" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A848" s="5"/>
-      <c r="K848" s="5">
-        <v>0</v>
-      </c>
-      <c r="L848" s="5">
-        <v>61</v>
-      </c>
-      <c r="M848" s="5"/>
-      <c r="N848" s="5"/>
-      <c r="O848" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A849" s="5"/>
-      <c r="K849" s="5">
-        <v>0</v>
-      </c>
-      <c r="L849" s="5">
-        <v>61</v>
-      </c>
-      <c r="M849" s="5"/>
-      <c r="N849" s="5"/>
-      <c r="O849" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="850" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A850" s="5"/>
-      <c r="K850" s="5">
-        <v>0</v>
-      </c>
-      <c r="L850" s="5">
-        <v>61</v>
-      </c>
-      <c r="M850" s="5"/>
-      <c r="N850" s="5"/>
-      <c r="O850" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="851" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A851" s="5"/>
-      <c r="K851" s="5">
-        <v>0</v>
-      </c>
-      <c r="L851" s="5">
-        <v>61</v>
-      </c>
-      <c r="M851" s="5"/>
-      <c r="N851" s="5"/>
-      <c r="O851" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="852" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A852" s="5"/>
-      <c r="K852" s="5">
-        <v>0</v>
-      </c>
-      <c r="L852" s="5">
-        <v>61</v>
-      </c>
-      <c r="M852" s="5"/>
-      <c r="N852" s="5"/>
-      <c r="O852" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="853" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A853" s="5"/>
-      <c r="K853" s="5">
-        <v>0</v>
-      </c>
-      <c r="L853" s="5">
-        <v>61</v>
-      </c>
-      <c r="M853" s="5"/>
-      <c r="N853" s="5"/>
-      <c r="O853" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="854" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A854" s="5"/>
-      <c r="K854" s="5">
-        <v>0</v>
-      </c>
-      <c r="L854" s="5">
-        <v>61</v>
-      </c>
-      <c r="M854" s="5"/>
-      <c r="N854" s="5"/>
-      <c r="O854" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="855" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A855" s="5"/>
-      <c r="K855" s="5">
-        <v>0</v>
-      </c>
-      <c r="L855" s="5">
-        <v>61</v>
-      </c>
-      <c r="M855" s="5"/>
-      <c r="N855" s="5"/>
-      <c r="O855" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A856" s="5"/>
-      <c r="K856" s="5">
-        <v>0</v>
-      </c>
-      <c r="L856" s="5">
-        <v>61</v>
-      </c>
-      <c r="M856" s="5"/>
-      <c r="N856" s="5"/>
-      <c r="O856" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="857" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A857" s="5"/>
-      <c r="K857" s="5">
-        <v>0</v>
-      </c>
-      <c r="L857" s="5">
-        <v>61</v>
-      </c>
-      <c r="M857" s="5"/>
-      <c r="N857" s="5"/>
-      <c r="O857" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A858" s="5"/>
-      <c r="K858" s="5">
-        <v>0</v>
-      </c>
-      <c r="L858" s="5">
-        <v>61</v>
-      </c>
-      <c r="M858" s="5"/>
-      <c r="N858" s="5"/>
-      <c r="O858" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="859" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A859" s="5"/>
-      <c r="K859" s="5">
-        <v>0</v>
-      </c>
-      <c r="L859" s="5">
-        <v>61</v>
-      </c>
-      <c r="M859" s="5"/>
-      <c r="N859" s="5"/>
-      <c r="O859" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="860" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A860" s="5"/>
-      <c r="K860" s="5">
-        <v>0</v>
-      </c>
-      <c r="L860" s="5">
-        <v>61</v>
-      </c>
-      <c r="M860" s="5"/>
-      <c r="N860" s="5"/>
-      <c r="O860" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="861" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A861" s="5"/>
-      <c r="K861" s="5">
-        <v>0</v>
-      </c>
-      <c r="L861" s="5">
-        <v>61</v>
-      </c>
-      <c r="M861" s="5"/>
-      <c r="N861" s="5"/>
-      <c r="O861" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="862" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A862" s="5"/>
-      <c r="K862" s="5">
-        <v>0</v>
-      </c>
-      <c r="L862" s="5">
-        <v>61</v>
-      </c>
-      <c r="M862" s="5"/>
-      <c r="N862" s="5"/>
-      <c r="O862" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A863" s="5"/>
-      <c r="K863" s="5">
-        <v>0</v>
-      </c>
-      <c r="L863" s="5">
-        <v>61</v>
-      </c>
-      <c r="M863" s="5"/>
-      <c r="N863" s="5"/>
-      <c r="O863" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="864" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A864" s="5"/>
-      <c r="K864" s="5">
-        <v>0</v>
-      </c>
-      <c r="L864" s="5">
-        <v>61</v>
-      </c>
-      <c r="M864" s="5"/>
-      <c r="N864" s="5"/>
-      <c r="O864" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="865" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A865" s="5"/>
-      <c r="K865" s="5">
-        <v>0</v>
-      </c>
-      <c r="L865" s="5">
-        <v>61</v>
-      </c>
-      <c r="M865" s="5"/>
-      <c r="N865" s="5"/>
-      <c r="O865" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="866" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A866" s="5"/>
-      <c r="K866" s="5">
-        <v>0</v>
-      </c>
-      <c r="L866" s="5">
-        <v>61</v>
-      </c>
-      <c r="M866" s="5"/>
-      <c r="N866" s="5"/>
-      <c r="O866" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="867" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A867" s="5"/>
-      <c r="K867" s="5">
-        <v>0</v>
-      </c>
-      <c r="L867" s="5">
-        <v>61</v>
-      </c>
-      <c r="M867" s="5"/>
-      <c r="N867" s="5"/>
-      <c r="O867" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="868" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A868" s="5"/>
-      <c r="K868" s="5">
-        <v>0</v>
-      </c>
-      <c r="L868" s="5">
-        <v>61</v>
-      </c>
-      <c r="M868" s="5"/>
-      <c r="N868" s="5"/>
-      <c r="O868" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="869" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A869" s="5"/>
-      <c r="K869" s="5">
-        <v>0</v>
-      </c>
-      <c r="L869" s="5">
-        <v>61</v>
-      </c>
-      <c r="M869" s="5"/>
-      <c r="N869" s="5"/>
-      <c r="O869" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="870" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A870" s="5"/>
-      <c r="K870" s="5">
-        <v>0</v>
-      </c>
-      <c r="L870" s="5">
-        <v>61</v>
-      </c>
-      <c r="M870" s="5"/>
-      <c r="N870" s="5"/>
-      <c r="O870" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="871" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A871" s="5"/>
-      <c r="K871" s="5">
-        <v>0</v>
-      </c>
-      <c r="L871" s="5">
-        <v>61</v>
-      </c>
-      <c r="M871" s="5"/>
-      <c r="N871" s="5"/>
-      <c r="O871" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="872" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A872" s="5"/>
-      <c r="K872" s="5">
-        <v>0</v>
-      </c>
-      <c r="L872" s="5">
-        <v>61</v>
-      </c>
-      <c r="M872" s="5"/>
-      <c r="N872" s="5"/>
-      <c r="O872" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="873" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A873" s="5"/>
-      <c r="K873" s="5">
-        <v>0</v>
-      </c>
-      <c r="L873" s="5">
-        <v>61</v>
-      </c>
-      <c r="M873" s="5"/>
-      <c r="N873" s="5"/>
-      <c r="O873" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="874" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A874" s="5"/>
-      <c r="K874" s="5">
-        <v>0</v>
-      </c>
-      <c r="L874" s="5">
-        <v>61</v>
-      </c>
-      <c r="M874" s="5"/>
-      <c r="N874" s="5"/>
-      <c r="O874" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="875" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A875" s="5"/>
-      <c r="K875" s="5">
-        <v>0</v>
-      </c>
-      <c r="L875" s="5">
-        <v>61</v>
-      </c>
-      <c r="M875" s="5"/>
-      <c r="N875" s="5"/>
-      <c r="O875" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="876" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A876" s="5"/>
-      <c r="K876" s="5">
-        <v>0</v>
-      </c>
-      <c r="L876" s="5">
-        <v>61</v>
-      </c>
-      <c r="M876" s="5"/>
-      <c r="N876" s="5"/>
-      <c r="O876" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="877" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A877" s="5"/>
-      <c r="K877" s="5">
-        <v>0</v>
-      </c>
-      <c r="L877" s="5">
-        <v>61</v>
-      </c>
-      <c r="M877" s="5"/>
-      <c r="N877" s="5"/>
-      <c r="O877" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="878" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A878" s="5"/>
-      <c r="K878" s="5">
-        <v>0</v>
-      </c>
-      <c r="L878" s="5">
-        <v>61</v>
-      </c>
-      <c r="M878" s="5"/>
-      <c r="N878" s="5"/>
-      <c r="O878" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="879" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A879" s="5"/>
-      <c r="K879" s="5">
-        <v>0</v>
-      </c>
-      <c r="L879" s="5">
-        <v>61</v>
-      </c>
-      <c r="M879" s="5"/>
-      <c r="N879" s="5"/>
-      <c r="O879" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="880" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A880" s="5"/>
-      <c r="K880" s="5">
-        <v>0</v>
-      </c>
-      <c r="L880" s="5">
-        <v>61</v>
-      </c>
-      <c r="M880" s="5"/>
-      <c r="N880" s="5"/>
-      <c r="O880" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="881" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A881" s="5"/>
-      <c r="K881" s="5">
-        <v>0</v>
-      </c>
-      <c r="L881" s="5">
-        <v>61</v>
-      </c>
-      <c r="M881" s="5"/>
-      <c r="N881" s="5"/>
-      <c r="O881" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="882" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A882" s="5"/>
-      <c r="K882" s="5">
-        <v>0</v>
-      </c>
-      <c r="L882" s="5">
-        <v>61</v>
-      </c>
-      <c r="M882" s="5"/>
-      <c r="N882" s="5"/>
-      <c r="O882" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="883" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A883" s="5"/>
-      <c r="K883" s="5">
-        <v>0</v>
-      </c>
-      <c r="L883" s="5">
-        <v>61</v>
-      </c>
-      <c r="M883" s="5"/>
-      <c r="N883" s="5"/>
-      <c r="O883" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="884" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A884" s="5"/>
-      <c r="K884" s="5">
-        <v>0</v>
-      </c>
-      <c r="L884" s="5">
-        <v>61</v>
-      </c>
-      <c r="M884" s="5"/>
-      <c r="N884" s="5"/>
-      <c r="O884" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="885" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A885" s="5"/>
-      <c r="K885" s="5">
-        <v>0</v>
-      </c>
-      <c r="L885" s="5">
-        <v>61</v>
-      </c>
-      <c r="M885" s="5"/>
-      <c r="N885" s="5"/>
-      <c r="O885" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="886" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A886" s="5"/>
-      <c r="K886" s="5">
-        <v>0</v>
-      </c>
-      <c r="L886" s="5">
-        <v>61</v>
-      </c>
-      <c r="M886" s="5"/>
-      <c r="N886" s="5"/>
-      <c r="O886" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="887" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A887" s="5"/>
-      <c r="K887" s="5">
-        <v>0</v>
-      </c>
-      <c r="L887" s="5">
-        <v>61</v>
-      </c>
-      <c r="M887" s="5"/>
-      <c r="N887" s="5"/>
-      <c r="O887" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="888" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A888" s="5"/>
-      <c r="K888" s="5">
-        <v>0</v>
-      </c>
-      <c r="L888" s="5">
-        <v>61</v>
-      </c>
-      <c r="M888" s="5"/>
-      <c r="N888" s="5"/>
-      <c r="O888" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="889" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A889" s="5"/>
-      <c r="K889" s="5">
-        <v>0</v>
-      </c>
-      <c r="L889" s="5">
-        <v>61</v>
-      </c>
-      <c r="M889" s="5"/>
-      <c r="N889" s="5"/>
-      <c r="O889" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="890" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A890" s="5"/>
-      <c r="K890" s="5">
-        <v>0</v>
-      </c>
-      <c r="L890" s="5">
-        <v>61</v>
-      </c>
-      <c r="M890" s="5"/>
-      <c r="N890" s="5"/>
-      <c r="O890" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="891" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A891" s="5"/>
-      <c r="K891" s="5">
-        <v>0</v>
-      </c>
-      <c r="L891" s="5">
-        <v>61</v>
-      </c>
-      <c r="M891" s="5"/>
-      <c r="N891" s="5"/>
-      <c r="O891" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="892" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A892" s="5"/>
-      <c r="K892" s="5">
-        <v>0</v>
-      </c>
-      <c r="L892" s="5">
-        <v>61</v>
-      </c>
-      <c r="M892" s="5"/>
-      <c r="N892" s="5"/>
-      <c r="O892" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="893" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A893" s="5"/>
-      <c r="K893" s="5">
-        <v>0</v>
-      </c>
-      <c r="L893" s="5">
-        <v>61</v>
-      </c>
-      <c r="M893" s="5"/>
-      <c r="N893" s="5"/>
-      <c r="O893" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="894" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A894" s="5"/>
-      <c r="K894" s="5">
-        <v>0</v>
-      </c>
-      <c r="L894" s="5">
-        <v>61</v>
-      </c>
-      <c r="M894" s="5"/>
-      <c r="N894" s="5"/>
-      <c r="O894" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="895" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A895" s="5"/>
-      <c r="K895" s="5">
-        <v>0</v>
-      </c>
-      <c r="L895" s="5">
-        <v>61</v>
-      </c>
-      <c r="M895" s="5"/>
-      <c r="N895" s="5"/>
-      <c r="O895" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="896" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A896" s="5"/>
-      <c r="K896" s="5">
-        <v>0</v>
-      </c>
-      <c r="L896" s="5">
-        <v>61</v>
-      </c>
-      <c r="M896" s="5"/>
-      <c r="N896" s="5"/>
-      <c r="O896" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="897" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A897" s="5"/>
-      <c r="K897" s="5">
-        <v>0</v>
-      </c>
-      <c r="L897" s="5">
-        <v>61</v>
-      </c>
-      <c r="M897" s="5"/>
-      <c r="N897" s="5"/>
-      <c r="O897" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="898" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A898" s="5"/>
-      <c r="K898" s="5">
-        <v>0</v>
-      </c>
-      <c r="L898" s="5">
-        <v>61</v>
-      </c>
-      <c r="M898" s="5"/>
-      <c r="N898" s="5"/>
-      <c r="O898" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="899" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A899" s="5"/>
-      <c r="K899" s="5">
-        <v>0</v>
-      </c>
-      <c r="L899" s="5">
-        <v>61</v>
-      </c>
-      <c r="M899" s="5"/>
-      <c r="N899" s="5"/>
-      <c r="O899" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="900" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A900" s="5"/>
-      <c r="K900" s="5">
-        <v>0</v>
-      </c>
-      <c r="L900" s="5">
-        <v>61</v>
-      </c>
-      <c r="M900" s="5"/>
-      <c r="N900" s="5"/>
-      <c r="O900" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="901" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A901" s="5"/>
-      <c r="K901" s="5">
-        <v>0</v>
-      </c>
-      <c r="L901" s="5">
-        <v>61</v>
-      </c>
-      <c r="M901" s="5"/>
-      <c r="N901" s="5"/>
-      <c r="O901" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="902" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A902" s="5"/>
-      <c r="K902" s="5">
-        <v>0</v>
-      </c>
-      <c r="L902" s="5">
-        <v>61</v>
-      </c>
-      <c r="M902" s="5"/>
-      <c r="N902" s="5"/>
-      <c r="O902" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="903" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A903" s="5"/>
-      <c r="K903" s="5">
-        <v>0</v>
-      </c>
-      <c r="L903" s="5">
-        <v>61</v>
-      </c>
-      <c r="M903" s="5"/>
-      <c r="N903" s="5"/>
-      <c r="O903" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A904" s="5"/>
-      <c r="K904" s="5">
-        <v>0</v>
-      </c>
-      <c r="L904" s="5">
-        <v>61</v>
-      </c>
-      <c r="M904" s="5"/>
-      <c r="N904" s="5"/>
-      <c r="O904" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="905" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A905" s="5"/>
-      <c r="K905" s="5">
-        <v>0</v>
-      </c>
-      <c r="L905" s="5">
-        <v>61</v>
-      </c>
-      <c r="M905" s="5"/>
-      <c r="N905" s="5"/>
-      <c r="O905" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="906" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A906" s="5"/>
-      <c r="K906" s="5">
-        <v>0</v>
-      </c>
-      <c r="L906" s="5">
-        <v>61</v>
-      </c>
-      <c r="M906" s="5"/>
-      <c r="N906" s="5"/>
-      <c r="O906" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="907" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A907" s="5"/>
-      <c r="K907" s="5">
-        <v>0</v>
-      </c>
-      <c r="L907" s="5">
-        <v>61</v>
-      </c>
-      <c r="M907" s="5"/>
-      <c r="N907" s="5"/>
-      <c r="O907" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="908" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A908" s="5"/>
-      <c r="K908" s="5">
-        <v>0</v>
-      </c>
-      <c r="L908" s="5">
-        <v>61</v>
-      </c>
-      <c r="M908" s="5"/>
-      <c r="N908" s="5"/>
-      <c r="O908" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="909" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A909" s="5"/>
-      <c r="K909" s="5">
-        <v>0</v>
-      </c>
-      <c r="L909" s="5">
-        <v>61</v>
-      </c>
-      <c r="M909" s="5"/>
-      <c r="N909" s="5"/>
-      <c r="O909" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="910" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A910" s="5"/>
-      <c r="K910" s="5">
-        <v>0</v>
-      </c>
-      <c r="L910" s="5">
-        <v>61</v>
-      </c>
-      <c r="M910" s="5"/>
-      <c r="N910" s="5"/>
-      <c r="O910" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="911" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A911" s="5"/>
-      <c r="K911" s="5">
-        <v>0</v>
-      </c>
-      <c r="L911" s="5">
-        <v>61</v>
-      </c>
-      <c r="M911" s="5"/>
-      <c r="N911" s="5"/>
-      <c r="O911" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="912" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A912" s="5"/>
-      <c r="K912" s="5">
-        <v>0</v>
-      </c>
-      <c r="L912" s="5">
-        <v>61</v>
-      </c>
-      <c r="M912" s="5"/>
-      <c r="N912" s="5"/>
-      <c r="O912" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="913" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A913" s="5"/>
-      <c r="K913" s="5">
-        <v>0</v>
-      </c>
-      <c r="L913" s="5">
-        <v>61</v>
-      </c>
-      <c r="M913" s="5"/>
-      <c r="N913" s="5"/>
-      <c r="O913" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="914" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A914" s="5"/>
-      <c r="K914" s="5">
-        <v>0</v>
-      </c>
-      <c r="L914" s="5">
-        <v>61</v>
-      </c>
-      <c r="M914" s="5"/>
-      <c r="N914" s="5"/>
-      <c r="O914" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="915" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A915" s="5"/>
-      <c r="K915" s="5">
-        <v>0</v>
-      </c>
-      <c r="L915" s="5">
-        <v>61</v>
-      </c>
-      <c r="M915" s="5"/>
-      <c r="N915" s="5"/>
-      <c r="O915" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="916" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A916" s="5"/>
-      <c r="K916" s="5">
-        <v>0</v>
-      </c>
-      <c r="L916" s="5">
-        <v>61</v>
-      </c>
-      <c r="M916" s="5"/>
-      <c r="N916" s="5"/>
-      <c r="O916" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="917" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A917" s="5"/>
-      <c r="K917" s="5">
-        <v>0</v>
-      </c>
-      <c r="L917" s="5">
-        <v>61</v>
-      </c>
-      <c r="M917" s="5"/>
-      <c r="N917" s="5"/>
-      <c r="O917" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="918" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A918" s="5"/>
-      <c r="K918" s="5">
-        <v>0</v>
-      </c>
-      <c r="L918" s="5">
-        <v>61</v>
-      </c>
-      <c r="M918" s="5"/>
-      <c r="N918" s="5"/>
-      <c r="O918" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="919" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A919" s="5"/>
-      <c r="K919" s="5">
-        <v>0</v>
-      </c>
-      <c r="L919" s="5">
-        <v>61</v>
-      </c>
-      <c r="M919" s="5"/>
-      <c r="N919" s="5"/>
-      <c r="O919" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="920" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A920" s="5"/>
-      <c r="K920" s="5">
-        <v>0</v>
-      </c>
-      <c r="L920" s="5">
-        <v>61</v>
-      </c>
-      <c r="M920" s="5"/>
-      <c r="N920" s="5"/>
-      <c r="O920" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="921" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A921" s="5"/>
-      <c r="K921" s="5">
-        <v>0</v>
-      </c>
-      <c r="L921" s="5">
-        <v>61</v>
-      </c>
-      <c r="M921" s="5"/>
-      <c r="N921" s="5"/>
-      <c r="O921" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="922" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A922" s="5"/>
-      <c r="K922" s="5">
-        <v>0</v>
-      </c>
-      <c r="L922" s="5">
-        <v>61</v>
-      </c>
-      <c r="M922" s="5"/>
-      <c r="N922" s="5"/>
-      <c r="O922" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="923" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A923" s="5"/>
-      <c r="K923" s="5">
-        <v>0</v>
-      </c>
-      <c r="L923" s="5">
-        <v>61</v>
-      </c>
-      <c r="M923" s="5"/>
-      <c r="N923" s="5"/>
-      <c r="O923" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="924" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A924" s="5"/>
-      <c r="K924" s="5">
-        <v>0</v>
-      </c>
-      <c r="L924" s="5">
-        <v>61</v>
-      </c>
-      <c r="M924" s="5"/>
-      <c r="N924" s="5"/>
-      <c r="O924" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="925" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A925" s="5"/>
-      <c r="K925" s="5">
-        <v>0</v>
-      </c>
-      <c r="L925" s="5">
-        <v>61</v>
-      </c>
-      <c r="M925" s="5"/>
-      <c r="N925" s="5"/>
-      <c r="O925" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="926" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A926" s="5"/>
-      <c r="K926" s="5">
-        <v>0</v>
-      </c>
-      <c r="L926" s="5">
-        <v>61</v>
-      </c>
-      <c r="M926" s="5"/>
-      <c r="N926" s="5"/>
-      <c r="O926" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="927" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A927" s="5"/>
-      <c r="K927" s="5">
-        <v>0</v>
-      </c>
-      <c r="L927" s="5">
-        <v>61</v>
-      </c>
-      <c r="M927" s="5"/>
-      <c r="N927" s="5"/>
-      <c r="O927" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="928" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A928" s="5"/>
-      <c r="K928" s="5">
-        <v>0</v>
-      </c>
-      <c r="L928" s="5">
-        <v>61</v>
-      </c>
-      <c r="M928" s="5"/>
-      <c r="N928" s="5"/>
-      <c r="O928" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="929" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A929" s="5"/>
-      <c r="K929" s="5">
-        <v>0</v>
-      </c>
-      <c r="L929" s="5">
-        <v>61</v>
-      </c>
-      <c r="M929" s="5"/>
-      <c r="N929" s="5"/>
-      <c r="O929" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="930" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A930" s="5"/>
-      <c r="K930" s="5">
-        <v>0</v>
-      </c>
-      <c r="L930" s="5">
-        <v>61</v>
-      </c>
-      <c r="M930" s="5"/>
-      <c r="N930" s="5"/>
-      <c r="O930" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="931" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A931" s="5"/>
-      <c r="K931" s="5">
-        <v>0</v>
-      </c>
-      <c r="L931" s="5">
-        <v>61</v>
-      </c>
-      <c r="M931" s="5"/>
-      <c r="N931" s="5"/>
-      <c r="O931" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="932" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A932" s="5"/>
-      <c r="K932" s="5">
-        <v>0</v>
-      </c>
-      <c r="L932" s="5">
-        <v>61</v>
-      </c>
-      <c r="M932" s="5"/>
-      <c r="N932" s="5"/>
-      <c r="O932" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="933" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A933" s="5"/>
-      <c r="K933" s="5">
-        <v>0</v>
-      </c>
-      <c r="L933" s="5">
-        <v>61</v>
-      </c>
-      <c r="M933" s="5"/>
-      <c r="N933" s="5"/>
-      <c r="O933" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="934" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A934" s="5"/>
-      <c r="K934" s="5">
-        <v>0</v>
-      </c>
-      <c r="L934" s="5">
-        <v>61</v>
-      </c>
-      <c r="M934" s="5"/>
-      <c r="N934" s="5"/>
-      <c r="O934" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="935" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A935" s="5"/>
-      <c r="K935" s="5">
-        <v>0</v>
-      </c>
-      <c r="L935" s="5">
-        <v>61</v>
-      </c>
-      <c r="M935" s="5"/>
-      <c r="N935" s="5"/>
-      <c r="O935" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="936" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A936" s="5"/>
-      <c r="K936" s="5">
-        <v>0</v>
-      </c>
-      <c r="L936" s="5">
-        <v>61</v>
-      </c>
-      <c r="M936" s="5"/>
-      <c r="N936" s="5"/>
-      <c r="O936" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="937" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A937" s="5"/>
-      <c r="K937" s="5">
-        <v>0</v>
-      </c>
-      <c r="L937" s="5">
-        <v>61</v>
-      </c>
-      <c r="M937" s="5"/>
-      <c r="N937" s="5"/>
-      <c r="O937" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="938" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A938" s="5"/>
-      <c r="K938" s="5">
-        <v>0</v>
-      </c>
-      <c r="L938" s="5">
-        <v>61</v>
-      </c>
-      <c r="M938" s="5"/>
-      <c r="N938" s="5"/>
-      <c r="O938" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="939" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A939" s="5"/>
-      <c r="K939" s="5">
-        <v>0</v>
-      </c>
-      <c r="L939" s="5">
-        <v>61</v>
-      </c>
-      <c r="M939" s="5"/>
-      <c r="N939" s="5"/>
-      <c r="O939" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="940" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A940" s="5"/>
-      <c r="K940" s="5">
-        <v>0</v>
-      </c>
-      <c r="L940" s="5">
-        <v>61</v>
-      </c>
-      <c r="M940" s="5"/>
-      <c r="N940" s="5"/>
-      <c r="O940" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="941" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A941" s="5"/>
-      <c r="K941" s="5">
-        <v>0</v>
-      </c>
-      <c r="L941" s="5">
-        <v>61</v>
-      </c>
-      <c r="M941" s="5"/>
-      <c r="N941" s="5"/>
-      <c r="O941" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="942" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A942" s="5"/>
-      <c r="K942" s="5">
-        <v>0</v>
-      </c>
-      <c r="L942" s="5">
-        <v>61</v>
-      </c>
-      <c r="M942" s="5"/>
-      <c r="N942" s="5"/>
-      <c r="O942" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="943" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A943" s="5"/>
-      <c r="K943" s="5">
-        <v>0</v>
-      </c>
-      <c r="L943" s="5">
-        <v>61</v>
-      </c>
-      <c r="M943" s="5"/>
-      <c r="N943" s="5"/>
-      <c r="O943" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="944" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A944" s="5"/>
-      <c r="K944" s="5">
-        <v>0</v>
-      </c>
-      <c r="L944" s="5">
-        <v>61</v>
-      </c>
-      <c r="M944" s="5"/>
-      <c r="N944" s="5"/>
-      <c r="O944" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="945" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A945" s="5"/>
-      <c r="K945" s="5">
-        <v>0</v>
-      </c>
-      <c r="L945" s="5">
-        <v>61</v>
-      </c>
-      <c r="M945" s="5"/>
-      <c r="N945" s="5"/>
-      <c r="O945" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="946" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A946" s="5"/>
-      <c r="K946" s="5">
-        <v>0</v>
-      </c>
-      <c r="L946" s="5">
-        <v>61</v>
-      </c>
-      <c r="M946" s="5"/>
-      <c r="N946" s="5"/>
-      <c r="O946" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="947" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A947" s="5"/>
-      <c r="K947" s="5">
-        <v>0</v>
-      </c>
-      <c r="L947" s="5">
-        <v>61</v>
-      </c>
-      <c r="M947" s="5"/>
-      <c r="N947" s="5"/>
-      <c r="O947" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="948" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A948" s="5"/>
-      <c r="K948" s="5">
-        <v>0</v>
-      </c>
-      <c r="L948" s="5">
-        <v>61</v>
-      </c>
-      <c r="M948" s="5"/>
-      <c r="N948" s="5"/>
-      <c r="O948" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="949" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A949" s="5"/>
-      <c r="K949" s="5">
-        <v>0</v>
-      </c>
-      <c r="L949" s="5">
-        <v>61</v>
-      </c>
-      <c r="M949" s="5"/>
-      <c r="N949" s="5"/>
-      <c r="O949" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="950" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A950" s="5"/>
-      <c r="K950" s="5">
-        <v>0</v>
-      </c>
-      <c r="L950" s="5">
-        <v>61</v>
-      </c>
-      <c r="M950" s="5"/>
-      <c r="N950" s="5"/>
-      <c r="O950" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="951" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A951" s="5"/>
-      <c r="K951" s="5">
-        <v>0</v>
-      </c>
-      <c r="L951" s="5">
-        <v>61</v>
-      </c>
-      <c r="M951" s="5"/>
-      <c r="N951" s="5"/>
-      <c r="O951" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="952" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A952" s="5"/>
-      <c r="K952" s="5">
-        <v>0</v>
-      </c>
-      <c r="L952" s="5">
-        <v>61</v>
-      </c>
-      <c r="M952" s="5"/>
-      <c r="N952" s="5"/>
-      <c r="O952" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="953" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A953" s="5"/>
-      <c r="K953" s="5">
-        <v>0</v>
-      </c>
-      <c r="L953" s="5">
-        <v>61</v>
-      </c>
-      <c r="M953" s="5"/>
-      <c r="N953" s="5"/>
-      <c r="O953" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="954" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A954" s="5"/>
-      <c r="K954" s="5">
-        <v>0</v>
-      </c>
-      <c r="L954" s="5">
-        <v>61</v>
-      </c>
-      <c r="M954" s="5"/>
-      <c r="N954" s="5"/>
-      <c r="O954" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="955" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A955" s="5"/>
-      <c r="K955" s="5">
-        <v>0</v>
-      </c>
-      <c r="L955" s="5">
-        <v>61</v>
-      </c>
-      <c r="M955" s="5"/>
-      <c r="N955" s="5"/>
-      <c r="O955" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="956" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A956" s="5"/>
-      <c r="K956" s="5">
-        <v>0</v>
-      </c>
-      <c r="L956" s="5">
-        <v>61</v>
-      </c>
-      <c r="M956" s="5"/>
-      <c r="N956" s="5"/>
-      <c r="O956" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="957" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A957" s="5"/>
-      <c r="K957" s="5">
-        <v>0</v>
-      </c>
-      <c r="L957" s="5">
-        <v>61</v>
-      </c>
-      <c r="M957" s="5"/>
-      <c r="N957" s="5"/>
-      <c r="O957" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="958" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A958" s="5"/>
-      <c r="K958" s="5">
-        <v>0</v>
-      </c>
-      <c r="L958" s="5">
-        <v>61</v>
-      </c>
-      <c r="M958" s="5"/>
-      <c r="N958" s="5"/>
-      <c r="O958" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="959" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A959" s="5"/>
-      <c r="K959" s="5">
-        <v>0</v>
-      </c>
-      <c r="L959" s="5">
-        <v>61</v>
-      </c>
-      <c r="M959" s="5"/>
-      <c r="N959" s="5"/>
-      <c r="O959" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="960" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A960" s="5"/>
-      <c r="K960" s="5">
-        <v>0</v>
-      </c>
-      <c r="L960" s="5">
-        <v>61</v>
-      </c>
-      <c r="M960" s="5"/>
-      <c r="N960" s="5"/>
-      <c r="O960" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="961" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A961" s="5"/>
-      <c r="K961" s="5">
-        <v>0</v>
-      </c>
-      <c r="L961" s="5">
-        <v>61</v>
-      </c>
-      <c r="M961" s="5"/>
-      <c r="N961" s="5"/>
-      <c r="O961" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="962" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A962" s="5"/>
-      <c r="K962" s="5">
-        <v>0</v>
-      </c>
-      <c r="L962" s="5">
-        <v>61</v>
-      </c>
-      <c r="M962" s="5"/>
-      <c r="N962" s="5"/>
-      <c r="O962" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="963" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A963" s="5"/>
-      <c r="K963" s="5">
-        <v>0</v>
-      </c>
-      <c r="L963" s="5">
-        <v>61</v>
-      </c>
-      <c r="M963" s="5"/>
-      <c r="N963" s="5"/>
-      <c r="O963" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="964" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A964" s="5"/>
-      <c r="K964" s="5">
-        <v>0</v>
-      </c>
-      <c r="L964" s="5">
-        <v>61</v>
-      </c>
-      <c r="M964" s="5"/>
-      <c r="N964" s="5"/>
-      <c r="O964" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="965" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A965" s="5"/>
-      <c r="K965" s="5">
-        <v>0</v>
-      </c>
-      <c r="L965" s="5">
-        <v>61</v>
-      </c>
-      <c r="M965" s="5"/>
-      <c r="N965" s="5"/>
-      <c r="O965" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="966" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A966" s="5"/>
-      <c r="K966" s="5">
-        <v>0</v>
-      </c>
-      <c r="L966" s="5">
-        <v>61</v>
-      </c>
-      <c r="M966" s="5"/>
-      <c r="N966" s="5"/>
-      <c r="O966" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="967" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A967" s="5"/>
-      <c r="K967" s="5">
-        <v>0</v>
-      </c>
-      <c r="L967" s="5">
-        <v>61</v>
-      </c>
-      <c r="M967" s="5"/>
-      <c r="N967" s="5"/>
-      <c r="O967" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>